--- a/docs/downloads/13/tbl_synthese_qualite_alaotra_mangabe.xlsx
+++ b/docs/downloads/13/tbl_synthese_qualite_alaotra_mangabe.xlsx
@@ -412,9 +412,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -471,9 +468,6 @@
         <is>
           <t>Mefiant</t>
         </is>
-      </c>
-      <c r="D6">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
